--- a/results/ai_run/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/ai_run/543_3/5_quantification/543_3_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.25</v>
+        <v>8.166700000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7447</v>
+        <v>4.324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.7387</v>
+        <v>4.0915</v>
       </c>
       <c r="D25" t="n">
-        <v>6.2331</v>
+        <v>3.569</v>
       </c>
       <c r="E25" t="n">
-        <v>7.0088</v>
+        <v>2.1734</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>414</v>
@@ -2631,7 +2631,7 @@
         <v>0.05300484</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.1406</v>
+        <v>3.3323</v>
       </c>
       <c r="Z2" t="n">
         <v>379</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>414</v>
@@ -2845,7 +2845,7 @@
         <v>0.05457341</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.4114</v>
+        <v>4.3291</v>
       </c>
       <c r="Z4" t="n">
         <v>392</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M5" t="n">
         <v>543</v>
@@ -2952,7 +2952,7 @@
         <v>0.03973386</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.0482</v>
+        <v>4.327</v>
       </c>
       <c r="Z5" t="n">
         <v>543</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>376</v>
@@ -3059,7 +3059,7 @@
         <v>0.0484685</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.7973</v>
+        <v>3.3986</v>
       </c>
       <c r="Z6" t="n">
         <v>365</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
         <v>425</v>
@@ -3166,7 +3166,7 @@
         <v>0.04859915</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.4409</v>
+        <v>4.9606</v>
       </c>
       <c r="Z7" t="n">
         <v>425</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>523</v>
@@ -3273,7 +3273,7 @@
         <v>0.0629907</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.6689</v>
+        <v>2.6164</v>
       </c>
       <c r="Z8" t="n">
         <v>466</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
         <v>320</v>
@@ -3380,7 +3380,7 @@
         <v>0.04771196</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.3348</v>
+        <v>2.6046</v>
       </c>
       <c r="Z9" t="n">
         <v>289</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>432</v>
@@ -3487,7 +3487,7 @@
         <v>0.04730656</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.7798</v>
+        <v>2.5199</v>
       </c>
       <c r="Z10" t="n">
         <v>413</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
         <v>330</v>
@@ -3594,7 +3594,7 @@
         <v>0.03705979</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5279</v>
+        <v>2.8814</v>
       </c>
       <c r="Z11" t="n">
         <v>257</v>
@@ -3662,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>193</v>
@@ -3701,7 +3701,7 @@
         <v>0.06057743</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5798</v>
+        <v>2.0966</v>
       </c>
       <c r="Z12" t="n">
         <v>153</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>333</v>
@@ -3787,7 +3787,7 @@
         <v>0.06327240000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>23.1794</v>
+        <v>10.5361</v>
       </c>
       <c r="Z13" t="n">
         <v>314</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
         <v>224</v>
@@ -3873,7 +3873,7 @@
         <v>0.04744526</v>
       </c>
       <c r="Y14" t="n">
-        <v>23.6833</v>
+        <v>3.7395</v>
       </c>
       <c r="Z14" t="n">
         <v>198</v>
